--- a/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:31</t>
+          <t>2026-09-01 03:32:16</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:32</t>
+          <t>2026-09-01 03:32:17</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:33</t>
+          <t>2026-09-01 03:32:18</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 03:15:35</t>
+          <t>2026-09-01 03:32:20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -509,16 +509,16 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-0.62%2405</t>
+          <t>+1.46%2440</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-0.62%</t>
+          <t>+1.46%</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>2405</v>
+        <v>2440</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -570,16 +570,16 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-1.46%7095</t>
+          <t>+9.94%7800</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1.46%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>7095</v>
+        <v>7800</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>-0.10%</t>
+          <t>+0.67%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -631,16 +631,16 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-1.51%3925</t>
+          <t>+9.94%4315</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-1.51%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>3925</v>
+        <v>4315</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -692,16 +692,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-2.58%755</t>
+          <t>+1.99%770</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-2.58%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>-0.15%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -753,16 +753,16 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.84%14180</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.84%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14180</v>
+        <v>14150</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -814,16 +814,16 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+1.94%447.5</t>
+          <t>+9.94%492</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+1.94%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>447.5</v>
+        <v>492</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -840,7 +840,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.09%</t>
+          <t>+0.47%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -875,16 +875,16 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>+8.28%7650</t>
+          <t>-0.92%7580</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>+8.28%</t>
+          <t>-0.92%</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>7650</v>
+        <v>7580</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>+0.29%</t>
+          <t>-0.04%</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -936,16 +936,16 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.09%5485</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5485</v>
+        <v>5640</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -962,7 +962,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -997,16 +997,16 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-2.49%1960</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-2.49%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>1960</v>
+        <v>2030</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1023,7 +1023,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1058,16 +1058,16 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-8.61%1380</t>
+          <t>+7.25%1480</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-8.61%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1380</v>
+        <v>1480</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.30%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1119,16 +1119,16 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+4.06%500</t>
+          <t>+7%535</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+4.06%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>500</v>
+        <v>535</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1180,16 +1180,16 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>+1.99%5130</t>
+          <t>+5.46%5410</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.46%</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>5130</v>
+        <v>5410</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1241,16 +1241,16 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+3.58%927</t>
+          <t>+3.34%958</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+3.58%</t>
+          <t>+3.34%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>927</v>
+        <v>958</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1302,16 +1302,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.24%2035</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-4.24%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>2035</v>
+        <v>2205</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:16</t>
+          <t>2026-09-01 15:28:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1363,16 +1363,16 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>+1.93%3425</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>+1.93%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>3425</v>
+        <v>3410</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>+0.05%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1424,16 +1424,16 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-6.17%912</t>
+          <t>+8.99%994</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-6.17%</t>
+          <t>+8.99%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>912</v>
+        <v>994</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>-0.13%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1485,16 +1485,16 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-3.94%305</t>
+          <t>-1.48%300.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-3.94%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>305</v>
+        <v>300.5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1511,7 +1511,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.08%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1546,16 +1546,16 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+1.2%677</t>
+          <t>+5.02%711</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+1.2%</t>
+          <t>+5.02%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>677</v>
+        <v>711</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1607,16 +1607,16 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.34%724</t>
+          <t>+6.77%773</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.34%</t>
+          <t>+6.77%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>724</v>
+        <v>773</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.11%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1668,16 +1668,16 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+9.91%477</t>
+          <t>+9.85%524</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+9.91%</t>
+          <t>+9.85%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>477</v>
+        <v>524</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.14%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1729,16 +1729,16 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-0.77%129</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-0.77%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>129</v>
+        <v>132.5</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1790,16 +1790,16 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+6.9%155</t>
+          <t>-0.65%154</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+6.9%</t>
+          <t>-0.65%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1851,16 +1851,16 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.38%183.5</t>
+          <t>-0.54%182.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.38%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>183.5</v>
+        <v>182.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1912,16 +1912,16 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+2.58%358</t>
+          <t>+0.28%359</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+2.58%</t>
+          <t>+0.28%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1973,16 +1973,16 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-3%178</t>
+          <t>+3.09%183.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>178</v>
+        <v>183.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1999,7 +1999,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2034,16 +2034,16 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-3.69%1435</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-3.69%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1435</v>
+        <v>1450</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2095,16 +2095,16 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.56%178</t>
+          <t>+2.53%182.5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-4.56%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>178</v>
+        <v>182.5</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2156,16 +2156,16 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-1.56%94.8</t>
+          <t>+0.42%95.2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-1.56%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>94.8</v>
+        <v>95.2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -2182,7 +2182,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2217,16 +2217,16 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+0.49%613</t>
+          <t>+1.79%624</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+0.49%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:17</t>
+          <t>2026-09-01 15:28:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2278,16 +2278,16 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0%178</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -2304,7 +2304,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2339,16 +2339,16 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+0.57%175</t>
+          <t>-1.14%173</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+0.57%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -2365,7 +2365,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2400,16 +2400,16 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-3.82%252</t>
+          <t>+1.59%256</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-3.82%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2461,16 +2461,16 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+2.78%16065</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+2.78%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>16065</v>
+        <v>17120</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2522,16 +2522,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-5.96%584</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-5.96%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>584</v>
+        <v>610</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2583,12 +2583,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.63%123.5</t>
+          <t>0%123.5</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-4.63%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H36" t="n">
@@ -2609,7 +2609,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2644,16 +2644,16 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-3.48%277</t>
+          <t>+2.53%284</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-3.48%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="H37" t="n">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>-0.04%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-7.11%1175</t>
+          <t>0%1175</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-7.11%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H38" t="n">
@@ -2731,7 +2731,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2766,16 +2766,16 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-0.46%433</t>
+          <t>-3%420</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-0.46%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>433</v>
+        <v>420</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2827,16 +2827,16 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+0.77%263</t>
+          <t>+4.94%276</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+0.77%</t>
+          <t>+4.94%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2888,16 +2888,16 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-0.8%864</t>
+          <t>+2.2%883</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-0.8%</t>
+          <t>+2.2%</t>
         </is>
       </c>
       <c r="H41" t="n">
-        <v>864</v>
+        <v>883</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2949,16 +2949,16 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-5.51%2400</t>
+          <t>+10%2640</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-5.51%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>2400</v>
+        <v>2640</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2975,7 +2975,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3010,16 +3010,16 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0%125.5</t>
+          <t>+1.59%127.5</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+1.59%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>125.5</v>
+        <v>127.5</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3071,16 +3071,16 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.31%254</t>
+          <t>-0.98%251.5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.31%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>254</v>
+        <v>251.5</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -3097,7 +3097,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3132,16 +3132,16 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>-1.52%485</t>
+          <t>+4.54%507</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>-1.52%</t>
+          <t>+4.54%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>485</v>
+        <v>507</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:18</t>
+          <t>2026-09-01 15:28:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3193,16 +3193,16 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>-5.01%275</t>
+          <t>+1.27%278.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>-5.01%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>275</v>
+        <v>278.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -3219,7 +3219,7 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3254,16 +3254,16 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>+2.19%65.4</t>
+          <t>+1.99%66.7</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+2.19%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H47" t="n">
-        <v>65.40000000000001</v>
+        <v>66.7</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3315,16 +3315,16 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>-2.33%50.2</t>
+          <t>+0.2%50.3</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>-2.33%</t>
+          <t>+0.2%</t>
         </is>
       </c>
       <c r="H48" t="n">
-        <v>50.2</v>
+        <v>50.3</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3376,16 +3376,16 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>-9.71%1395</t>
+          <t>-6.09%1310</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>-9.71%</t>
+          <t>-6.09%</t>
         </is>
       </c>
       <c r="H49" t="n">
-        <v>1395</v>
+        <v>1310</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3437,16 +3437,16 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>-0.95%47.1</t>
+          <t>+0.96%47.55</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>-0.95%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>47.1</v>
+        <v>47.55</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3498,16 +3498,16 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>+1.41%6100</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>6100</v>
+        <v>5995</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3559,16 +3559,16 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>+7.55%1140</t>
+          <t>-1.75%1120</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>+7.55%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1140</v>
+        <v>1120</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -3585,7 +3585,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3620,16 +3620,16 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>-0.81%1230</t>
+          <t>-0.41%1225</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>-0.81%</t>
+          <t>-0.41%</t>
         </is>
       </c>
       <c r="H53" t="n">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3681,16 +3681,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>-2.56%171.5</t>
+          <t>+0.58%172.5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>-2.56%</t>
+          <t>+0.58%</t>
         </is>
       </c>
       <c r="H54" t="n">
-        <v>171.5</v>
+        <v>172.5</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3742,16 +3742,16 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-0.55%540</t>
+          <t>-2.59%526</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-0.55%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>540</v>
+        <v>526</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3803,16 +3803,16 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>-3.44%729</t>
+          <t>+4.39%761</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>-3.44%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>729</v>
+        <v>761</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -3829,7 +3829,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3864,16 +3864,16 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>0%144</t>
+          <t>+0.69%145</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H57" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 03:32:20</t>
+          <t>2026-09-01 15:28:51</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -3925,16 +3925,16 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>+0.73%48.55</t>
+          <t>-0.1%48.5</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>+0.73%</t>
+          <t>-0.1%</t>
         </is>
       </c>
       <c r="H58" t="n">
-        <v>48.55</v>
+        <v>48.5</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>

--- a/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:47</t>
+          <t>2026-09-01 15:55:39</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:48</t>
+          <t>2026-09-01 15:55:40</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:49</t>
+          <t>2026-09-01 15:55:41</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 15:28:51</t>
+          <t>2026-09-01 15:55:43</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:39</t>
+          <t>2026-09-01 16:15:03</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:40</t>
+          <t>2026-09-01 16:15:04</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:41</t>
+          <t>2026-09-01 16:15:05</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 15:55:43</t>
+          <t>2026-09-01 16:15:07</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.47%1,794,000</t>
+          <t>8.26%1,794,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.47%</t>
+          <t>8.26%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -535,7 +535,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7.11%510,000</t>
+          <t>7.51%510,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>7.11%</t>
+          <t>7.51%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.67%</t>
+          <t>+0.71%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5.72%742,000</t>
+          <t>6.04%742,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>6.04%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -657,7 +657,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>+0.54%</t>
+          <t>+0.57%</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.63%3,800,000</t>
+          <t>5.52%3,800,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.63%</t>
+          <t>5.52%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -748,38 +748,38 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2059川湖</t>
+          <t>3105穩懋</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-0.21%14150</t>
+          <t>+9.94%492</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-0.21%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>14150</v>
+        <v>492</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.12%184,000</t>
+          <t>5.30%5,709,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.12%</t>
+          <t>5.30%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>184000</v>
+        <v>5709000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.50%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -809,38 +809,38 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3105穩懋</t>
+          <t>2059川湖</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>+9.94%492</t>
+          <t>-0.21%14150</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>-0.21%</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>492</v>
+        <v>14150</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>5.02%5,709,000</t>
+          <t>4.91%184,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.02%</t>
+          <t>4.91%</t>
         </is>
       </c>
       <c r="K7" t="n">
-        <v>5709000</v>
+        <v>184000</v>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>+0.47%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3.83%255,000</t>
+          <t>3.65%255,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>3.83%</t>
+          <t>3.65%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3.41%317,000</t>
+          <t>3.38%317,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>3.41%</t>
+          <t>3.38%</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>2360致茂</t>
+          <t>3491昇達科</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>+3.57%2030</t>
+          <t>+7.25%1480</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>+3.57%</t>
+          <t>+7.25%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>2030</v>
+        <v>1480</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3.22%837,000</t>
+          <t>3.30%1,180,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.30%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>837000</v>
+        <v>1180000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>+0.12%</t>
+          <t>+0.23%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1053,38 +1053,38 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>3491昇達科</t>
+          <t>4958臻鼎-KY</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>+7.25%1480</t>
+          <t>+7%535</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>+7.25%</t>
+          <t>+7%</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>1480</v>
+        <v>535</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.20%1,180,000</t>
+          <t>3.21%3,178,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K11" t="n">
-        <v>1180000</v>
+        <v>3178000</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.22%</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1114,38 +1114,38 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>4958臻鼎-KY</t>
+          <t>2360致茂</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>+7%535</t>
+          <t>+3.57%2030</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>+7%</t>
+          <t>+3.57%</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>535</v>
+        <v>2030</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3.12%3,178,000</t>
+          <t>3.21%837,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>3.12%</t>
+          <t>3.21%</t>
         </is>
       </c>
       <c r="K12" t="n">
-        <v>3178000</v>
+        <v>837000</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.21%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.09%307,000</t>
+          <t>3.14%307,000</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>3.09%</t>
+          <t>3.14%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1254,12 +1254,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3.00%1,650,000</t>
+          <t>2.98%1,650,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>3.00%</t>
+          <t>2.98%</t>
         </is>
       </c>
       <c r="K14" t="n">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1315,20 +1315,20 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.90%727,000</t>
+          <t>2.61%627,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.90%</t>
+          <t>2.61%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>727000</v>
+        <v>627000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.23%</t>
+          <t>+0.21%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:03</t>
+          <t>2026-09-01 17:53:43</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1376,12 +1376,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.53%376,000</t>
+          <t>2.42%376,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.53%</t>
+          <t>2.42%</t>
         </is>
       </c>
       <c r="K16" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1437,12 +1437,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.98%1,108,000</t>
+          <t>2.08%1,108,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.08%</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>+0.18%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,38 +1480,38 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2301光寶科</t>
+          <t>2395研華</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-1.48%300.5</t>
+          <t>+5.02%711</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+5.02%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>300.5</v>
+        <v>711</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.96%3,273,000</t>
+          <t>1.98%1,473,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.98%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>3273000</v>
+        <v>1473000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2395研華</t>
+          <t>2301光寶科</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+5.02%711</t>
+          <t>-1.48%300.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+5.02%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>711</v>
+        <v>300.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.96%1,473,000</t>
+          <t>1.86%3,273,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.96%</t>
+          <t>1.86%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>1473000</v>
+        <v>3273000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1620,12 +1620,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.65%1,158,000</t>
+          <t>1.69%1,158,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.65%</t>
+          <t>1.69%</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1681,12 +1681,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.46%1,562,000</t>
+          <t>1.54%1,562,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.54%</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1742,12 +1742,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.33%5,243,000</t>
+          <t>1.31%5,243,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.33%</t>
+          <t>1.31%</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1803,12 +1803,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.32%4,353,000</t>
+          <t>1.27%4,353,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.27%</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6214精誠</t>
+          <t>5483中美晶</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-0.54%182.5</t>
+          <t>+3.09%183.5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-0.54%</t>
+          <t>+3.09%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>182.5</v>
+        <v>183.5</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.26%3,494,000</t>
+          <t>1.21%3,506,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>3494000</v>
+        <v>3506000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.26%1,786,000</t>
+          <t>1.21%1,786,000</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.26%</t>
+          <t>1.21%</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>5483中美晶</t>
+          <t>6214精誠</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>+3.09%183.5</t>
+          <t>-0.54%182.5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>+3.09%</t>
+          <t>-0.54%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>183.5</v>
+        <v>182.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.23%3,506,000</t>
+          <t>1.20%3,494,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.23%</t>
+          <t>1.20%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>3506000</v>
+        <v>3494000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>6274台燿</t>
+          <t>3265台星科</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>+2.53%182.5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+2.53%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>1450</v>
+        <v>182.5</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.21%431,000</t>
+          <t>1.19%3,445,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.21%</t>
+          <t>1.19%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>431000</v>
+        <v>3445000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3265台星科</t>
+          <t>6274台燿</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+2.53%182.5</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+2.53%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>182.5</v>
+        <v>1450</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.20%3,445,000</t>
+          <t>1.18%431,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3445000</v>
+        <v>431000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5425台半</t>
+          <t>2467志聖</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>+0.42%95.2</t>
+          <t>+1.79%624</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>+0.42%</t>
+          <t>+1.79%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>95.2</v>
+        <v>624</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.20%6,468,000</t>
+          <t>1.18%1,000,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.18%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>6468000</v>
+        <v>1000000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,38 +2212,38 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>2467志聖</t>
+          <t>3231緯創</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+1.79%624</t>
+          <t>+2.25%182</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.79%</t>
+          <t>+2.25%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>624</v>
+        <v>182</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.20%1,000,000</t>
+          <t>1.17%3,405,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.20%</t>
+          <t>1.17%</t>
         </is>
       </c>
       <c r="K30" t="n">
-        <v>1000000</v>
+        <v>3405000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:04</t>
+          <t>2026-09-01 17:53:45</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,38 +2273,38 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>3231緯創</t>
+          <t>5425台半</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+2.25%182</t>
+          <t>+0.42%95.2</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+2.25%</t>
+          <t>+0.42%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>182</v>
+        <v>95.2</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1.19%3,405,000</t>
+          <t>1.16%6,468,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1.19%</t>
+          <t>1.16%</t>
         </is>
       </c>
       <c r="K31" t="n">
-        <v>3405000</v>
+        <v>6468000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,25 +2334,25 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>5274信驊</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-1.14%173</t>
+          <t>+6.57%17120</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+6.57%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>173</v>
+        <v>17120</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.16%3,371,000</t>
+          <t>1.16%35,900</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2361,11 +2361,11 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>3371000</v>
+        <v>35900</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2413,12 +2413,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1.16%2,337,000</t>
+          <t>1.13%2,337,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.13%</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5274信驊</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+6.57%17120</t>
+          <t>-1.14%173</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+6.57%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>17120</v>
+        <v>173</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.13%35,900</t>
+          <t>1.10%3,371,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.13%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>35900</v>
+        <v>3371000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>1.08%4,451,000</t>
+          <t>1.04%4,451,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1.08%</t>
+          <t>1.04%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>1.04%1,910,000</t>
+          <t>1.02%1,910,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.88%382,000</t>
+          <t>0.85%382,000</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.85%</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>6472保瑞</t>
+          <t>2486一詮</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-3%420</t>
+          <t>+4.94%276</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-3%</t>
+          <t>+4.94%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>420</v>
+        <v>276</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.88%1,032,000</t>
+          <t>0.84%1,607,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.88%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>1032000</v>
+        <v>1607000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2486一詮</t>
+          <t>6472保瑞</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>+4.94%276</t>
+          <t>-3%420</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+4.94%</t>
+          <t>-3%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>276</v>
+        <v>420</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.83%1,607,000</t>
+          <t>0.82%1,032,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>1607000</v>
+        <v>1032000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.78%459,000</t>
+          <t>0.77%459,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.44%93,000</t>
+          <t>0.46%93,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.44%</t>
+          <t>0.46%</t>
         </is>
       </c>
       <c r="K42" t="n">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3023,12 +3023,12 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.32%1,294,000</t>
+          <t>0.31%1,294,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K43" t="n">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,25 +3066,25 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>3617碩天</t>
+          <t>6196帆宣</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>-0.98%251.5</t>
+          <t>+4.54%507</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>-0.98%</t>
+          <t>+4.54%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>251.5</v>
+        <v>507</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.29%591,000</t>
+          <t>0.29%307,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3093,11 +3093,11 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>591000</v>
+        <v>307000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3127,38 +3127,38 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>6196帆宣</t>
+          <t>6672騰輝電子-KY</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>+4.54%507</t>
+          <t>+1.27%278.5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+4.54%</t>
+          <t>+1.27%</t>
         </is>
       </c>
       <c r="H45" t="n">
-        <v>507</v>
+        <v>278.5</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.29%307,000</t>
+          <t>0.28%541,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K45" t="n">
-        <v>307000</v>
+        <v>541000</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:05</t>
+          <t>2026-09-01 17:53:46</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3188,38 +3188,38 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>6672騰輝電子-KY</t>
+          <t>3617碩天</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>+1.27%278.5</t>
+          <t>-0.98%251.5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.27%</t>
+          <t>-0.98%</t>
         </is>
       </c>
       <c r="H46" t="n">
-        <v>278.5</v>
+        <v>251.5</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.29%541,000</t>
+          <t>0.28%591,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.29%</t>
+          <t>0.28%</t>
         </is>
       </c>
       <c r="K46" t="n">
-        <v>541000</v>
+        <v>591000</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3328,12 +3328,12 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>0.28%2,839,000</t>
+          <t>0.27%2,839,000</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>0.28%</t>
+          <t>0.27%</t>
         </is>
       </c>
       <c r="K48" t="n">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3389,12 +3389,12 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.12%42,000</t>
+          <t>0.10%42,000</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.12%</t>
+          <t>0.10%</t>
         </is>
       </c>
       <c r="K49" t="n">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3432,38 +3432,38 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6177達麗</t>
+          <t>6640均華</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>+0.96%47.55</t>
+          <t>-1.75%1120</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>+0.96%</t>
+          <t>-1.75%</t>
         </is>
       </c>
       <c r="H50" t="n">
-        <v>47.55</v>
+        <v>1120</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.02%194,350</t>
+          <t>0.03%13,000</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.02%</t>
+          <t>0.03%</t>
         </is>
       </c>
       <c r="K50" t="n">
-        <v>194350</v>
+        <v>13000</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3493,38 +3493,38 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>6177達麗</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>+0.96%47.55</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>+0.96%</t>
         </is>
       </c>
       <c r="H51" t="n">
-        <v>5995</v>
+        <v>47.55</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.01%1,000</t>
+          <t>0.02%194,350</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.01%</t>
+          <t>0.02%</t>
         </is>
       </c>
       <c r="K51" t="n">
-        <v>1000</v>
+        <v>194350</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3554,34 +3554,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6640均華</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>-1.75%1120</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>-1.75%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H52" t="n">
-        <v>1120</v>
+        <v>5995</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>&lt;0.01%3,000</t>
+          <t>0.01%1,000</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>&lt;0.01%</t>
+          <t>0.01%</t>
         </is>
       </c>
       <c r="K52" t="n">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3737,25 +3737,25 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>8358金居</t>
+          <t>1519華城</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>-2.59%526</t>
+          <t>+4.39%761</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>-2.59%</t>
+          <t>+4.39%</t>
         </is>
       </c>
       <c r="H55" t="n">
-        <v>526</v>
+        <v>761</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>&lt;0.01%1,000</t>
+          <t>&lt;0.01%660</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -3764,11 +3764,11 @@
         </is>
       </c>
       <c r="K55" t="n">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3798,25 +3798,25 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1519華城</t>
+          <t>8358金居</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>+4.39%761</t>
+          <t>-2.59%526</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>+4.39%</t>
+          <t>-2.59%</t>
         </is>
       </c>
       <c r="H56" t="n">
-        <v>761</v>
+        <v>526</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>&lt;0.01%660</t>
+          <t>&lt;0.01%1,000</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -3825,11 +3825,11 @@
         </is>
       </c>
       <c r="K56" t="n">
-        <v>660</v>
+        <v>1000</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 16:15:07</t>
+          <t>2026-09-01 17:53:47</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">

--- a/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00982A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:43</t>
+          <t>2026-09-01 20:34:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:45</t>
+          <t>2026-09-01 20:34:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:46</t>
+          <t>2026-09-01 20:34:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -3297,7 +3297,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -3358,7 +3358,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -3602,7 +3602,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3785,7 +3785,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -3907,7 +3907,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2026-09-01 17:53:47</t>
+          <t>2026-09-01 20:34:26</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
